--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_06-08-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_06-08-2025.xlsx
@@ -589,27 +589,27 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -659,78 +659,78 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>£17.95</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>£12.62</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>£12.62</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>£12.62</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>£17.95</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>£17.39 presale price: £26.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>£12.62</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>£12.62</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>£12.62</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>£17.39 presale price: £26.0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>£12.33</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>£12.62</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -780,78 +780,78 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>£15.75</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>£15.75</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>£21.95</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>£15.99</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>£16.18</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>£15.55</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>£20.60 presale price: £30.03</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>£15.75</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>£16.18</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>£21.95</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>£15.99</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>£16.18</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>£15.55</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>£20.60 presale price: £30.03</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>£15.75</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>£16.18</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -901,34 +901,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>£16.50</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>£20.95</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>£16.60</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>£16.60</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>£16.60</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>£20.95</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>£16.60</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>£16.60</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>£16.70</t>
@@ -952,27 +952,27 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1022,78 +1022,78 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>£21.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>£21.00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>£21.00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>£26.95</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>£21.05</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>£21.08</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>£21.00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>£26.99 presale price: £39.44</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>£20.60</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>£21.08</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>£21.08</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>£26.95</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>£21.05</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>£21.08</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>£21.00</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>£26.99 presale price: £39.44</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>£20.60</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>£21.08</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1194,27 +1194,27 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1315,27 +1315,27 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1385,39 +1385,39 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>£26.40</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>£26.40</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>£26.40</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>£34.95</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>£26.45</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>£26.50</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>£26.50</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>£26.50</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>£34.95</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>£26.45</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>£26.50</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>£26.50</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>£35.35 presale price: £52.32</t>
@@ -1436,27 +1436,27 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1506,78 +1506,78 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>£28.80</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>£28.80</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>£28.80</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>£35.95</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>£28.80</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>£28.82</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>£28.58</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>£38.75 presale price: £56.64</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>£27.95</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>£28.82</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>£28.82</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>£35.95</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>£28.80</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>£28.82</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>£28.58</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>£38.75 presale price: £56.64</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>£27.95</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>£28.82</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1627,39 +1627,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>£28.35</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>£28.35</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>£28.35</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>£35.95</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>£28.60</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>£28.50</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>£28.50</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>£28.50</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>£35.95</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>£28.60</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>£28.50</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>£28.50</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>£29.16 presale price: £46.38</t>
@@ -1678,27 +1678,27 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1799,27 +1799,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1869,39 +1869,39 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>£34.90</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>£34.90</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>£34.90</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>£44.50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>£34.95</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>£34.99</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>£34.99</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>£34.99</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>£44.50</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>£34.95</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>£34.99</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>£34.99</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>£43.99 presale price: £72.38</t>
@@ -1920,27 +1920,27 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2041,27 +2041,27 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2162,27 +2162,27 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2283,27 +2283,27 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2501,27 +2501,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2622,27 +2622,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2743,27 +2743,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2864,27 +2864,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2985,27 +2985,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f54ae415+77285]
-	GetHandleVerifier [0x0x7ff6f54ae470+77376]
-	(No symbol) [0x0x7ff6f5279a6a]
-	(No symbol) [0x0x7ff6f52d0406]
-	(No symbol) [0x0x7ff6f52d06bc]
-	(No symbol) [0x0x7ff6f5323ac7]
-	(No symbol) [0x0x7ff6f52f864f]
-	(No symbol) [0x0x7ff6f532087f]
-	(No symbol) [0x0x7ff6f52f83e3]
-	(No symbol) [0x0x7ff6f52c1521]
-	(No symbol) [0x0x7ff6f52c22b3]
-	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
-	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
-	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
-	GetHandleVerifier [0x0x7ff6f54c884e+184862]
-	GetHandleVerifier [0x0x7ff6f54d055f+216879]
-	GetHandleVerifier [0x0x7ff6f54b7084+113236]
-	GetHandleVerifier [0x0x7ff6f54b7239+113673]
-	GetHandleVerifier [0x0x7ff6f549e298+11368]
+	GetHandleVerifier [0x0x7ff74b706b55+79621]
+	GetHandleVerifier [0x0x7ff74b706bb0+79712]
+	(No symbol) [0x0x7ff74b49c0ea]
+	(No symbol) [0x0x7ff74b4f2f56]
+	(No symbol) [0x0x7ff74b4f320c]
+	(No symbol) [0x0x7ff74b5465b7]
+	(No symbol) [0x0x7ff74b51b17f]
+	(No symbol) [0x0x7ff74b5433d0]
+	(No symbol) [0x0x7ff74b51af13]
+	(No symbol) [0x0x7ff74b4e4151]
+	(No symbol) [0x0x7ff74b4e4ee3]
+	GetHandleVerifier [0x0x7ff74b9c686d+2962461]
+	GetHandleVerifier [0x0x7ff74b9c0b8d+2938685]
+	GetHandleVerifier [0x0x7ff74b9df74d+3064573]
+	GetHandleVerifier [0x0x7ff74b720c9e+186446]
+	GetHandleVerifier [0x0x7ff74b728a6f+218655]
+	GetHandleVerifier [0x0x7ff74b70f944+115956]
+	GetHandleVerifier [0x0x7ff74b70faf9+116393]
+	GetHandleVerifier [0x0x7ff74b6f5f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
